--- a/九龙-何文田-VAU Residence/VAU Residence_销控明细表.xlsx
+++ b/九龙-何文田-VAU Residence/VAU Residence_销控明细表.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2022-01-18</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2022-03-02</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
+          <t>2022-01-27</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11210,7 +11210,7 @@
           <t>F | 384呎 (2房)
 $1306万
 $34,000/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -11218,7 +11218,7 @@
           <t>G | 499呎 (3房)
 $1697万
 $34,000/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr"/>
@@ -11234,7 +11234,7 @@
           <t>A | 282呎 (1房)
 $778万
 $27,603/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -11242,7 +11242,7 @@
           <t>B | 278呎 (1房)
 $766万
 $27,543/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -11250,7 +11250,7 @@
           <t>C | 264呎 (1房)
 $779万
 $29,504/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -11258,7 +11258,7 @@
           <t>D | 210呎 (开放式)
 $581万
 $27,667/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -11266,7 +11266,7 @@
           <t>E | 209呎 (开放式)
 $618万
 $29,589/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -11274,7 +11274,7 @@
           <t>F | 384呎 (2房)
 $1039万
 $27,062/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -11282,7 +11282,7 @@
           <t>G | 499呎 (3房)
 $1272万
 $25,497/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr"/>
@@ -11306,7 +11306,7 @@
           <t>B | 278呎 (1房)
 $670万
 $24,086/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -11314,7 +11314,7 @@
           <t>C | 264呎 (1房)
 $714万
 $27,061/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -11322,7 +11322,7 @@
           <t>D | 210呎 (开放式)
 $504万
 $24,014/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -11330,7 +11330,7 @@
           <t>E | 209呎 (开放式)
 $480万
 $22,967/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -11338,7 +11338,7 @@
           <t>F | 384呎 (2房)
 $1164万
 $30,320/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -11362,7 +11362,7 @@
           <t>A | 282呎 (1房)
 $632万
 $22,429/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -11370,7 +11370,7 @@
           <t>B | 278呎 (1房)
 $601万
 $21,615/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -11378,7 +11378,7 @@
           <t>C | 264呎 (1房)
 $592万
 $22,420/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -11386,7 +11386,7 @@
           <t>D | 210呎 (开放式)
 $470万
 $22,390/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -11394,7 +11394,7 @@
           <t>E | 209呎 (开放式)
 $679万
 $32,507/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -11402,7 +11402,7 @@
           <t>F | 285呎 (1房)
 $862万
 $30,263/呎
-(23年-05月-11日)</t>
+(23年-05月-12日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -11410,7 +11410,7 @@
           <t>G | 211呎 (开放式)
 $488万
 $23,147/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -11418,7 +11418,7 @@
           <t>H | 388呎 (2房)
 $855万
 $22,039/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
           <t>A | 282呎 (1房)
 $591万
 $20,961/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -11441,7 +11441,7 @@
           <t>B | 278呎 (1房)
 $592万
 $21,277/呎
-(24年-09月-02日)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -11449,7 +11449,7 @@
           <t>C | 264呎 (1房)
 $579万
 $21,928/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -11457,7 +11457,7 @@
           <t>D | 210呎 (开放式)
 $480万
 $22,833/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -11465,7 +11465,7 @@
           <t>E | 209呎 (开放式)
 $479万
 $22,900/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -11473,7 +11473,7 @@
           <t>F | 285呎 (1房)
 $860万
 $30,172/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -11481,7 +11481,7 @@
           <t>G | 211呎 (开放式)
 $522万
 $24,749/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -11489,7 +11489,7 @@
           <t>H | 388呎 (2房)
 $847万
 $21,820/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
           <t>B | 278呎 (1房)
 $664万
 $23,874/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -11520,7 +11520,7 @@
           <t>C | 264呎 (1房)
 $572万
 $21,667/呎
-(24年-06月-19日)</t>
+(24年-06月-20日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -11528,7 +11528,7 @@
           <t>D | 210呎 (开放式)
 $456万
 $21,719/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -11536,7 +11536,7 @@
           <t>E | 209呎 (开放式)
 $451万
 $21,579/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -11544,7 +11544,7 @@
           <t>F | 285呎 (1房)
 $767万
 $26,926/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -11552,7 +11552,7 @@
           <t>G | 211呎 (开放式)
 $641万
 $30,370/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -11560,7 +11560,7 @@
           <t>H | 388呎 (2房)
 $875万
 $22,541/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
           <t>A | 282呎 (1房)
 $577万
 $20,465/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11583,7 +11583,7 @@
           <t>B | 278呎 (1房)
 $578万
 $20,773/呎
-(24年-08月-25日)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -11591,7 +11591,7 @@
           <t>C | 264呎 (1房)
 $565万
 $21,413/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -11599,7 +11599,7 @@
           <t>D | 210呎 (开放式)
 $451万
 $21,462/呎
-(25年-01月-22日)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -11607,7 +11607,7 @@
           <t>E | 209呎 (开放式)
 $446万
 $21,316/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -11615,7 +11615,7 @@
           <t>F | 285呎 (1房)
 $840万
 $29,488/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -11623,7 +11623,7 @@
           <t>G | 211呎 (开放式)
 $468万
 $22,194/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -11631,7 +11631,7 @@
           <t>H | 388呎 (2房)
 $830万
 $21,387/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
           <t>A | 282呎 (1房)
 $627万
 $22,245/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -11654,7 +11654,7 @@
           <t>B | 278呎 (1房)
 $660万
 $23,730/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -11662,7 +11662,7 @@
           <t>C | 264呎 (1房)
 $786万
 $29,754/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -11670,7 +11670,7 @@
           <t>D | 210呎 (开放式)
 $445万
 $21,210/呎
-(25年-01月-12日)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -11678,7 +11678,7 @@
           <t>E | 209呎 (开放式)
 $474万
 $22,694/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -11686,7 +11686,7 @@
           <t>F | 285呎 (1房)
 $786万
 $27,568/呎
-(22年-05月-02日)</t>
+(22年-05月-03日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -11694,7 +11694,7 @@
           <t>G | 211呎 (开放式)
 $672万
 $31,834/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -11702,7 +11702,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
     </row>
@@ -11717,7 +11717,7 @@
           <t>A | 282呎 (1房)
 $635万
 $22,511/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11725,7 +11725,7 @@
           <t>B | 278呎 (1房)
 $785万
 $28,248/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -11733,7 +11733,7 @@
           <t>C | 264呎 (1房)
 $624万
 $23,652/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -11741,7 +11741,7 @@
           <t>D | 210呎 (开放式)
 $474万
 $22,562/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -11749,7 +11749,7 @@
           <t>E | 209呎 (开放式)
 $496万
 $23,718/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -11757,7 +11757,7 @@
           <t>F | 285呎 (1房)
 $739万
 $25,923/呎
-(23年-01月-10日)</t>
+(23年-01月-11日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -11765,7 +11765,7 @@
           <t>G | 211呎 (开放式)
 $516万
 $24,455/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -11773,7 +11773,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11788,7 @@
           <t>A | 282呎 (1房)
 $596万
 $21,121/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -11796,7 +11796,7 @@
           <t>B | 278呎 (1房)
 $563万
 $20,259/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -11804,7 +11804,7 @@
           <t>C | 264呎 (1房)
 $551万
 $20,886/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -11812,7 +11812,7 @@
           <t>D | 210呎 (开放式)
 $472万
 $22,495/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -11820,7 +11820,7 @@
           <t>E | 209呎 (开放式)
 $471万
 $22,555/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -11828,7 +11828,7 @@
           <t>F | 285呎 (1房)
 $730万
 $25,600/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -11836,7 +11836,7 @@
           <t>G | 211呎 (开放式)
 $648万
 $30,735/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -11844,7 +11844,7 @@
           <t>H | 388呎 (2房)
 $821万
 $21,170/呎
-(24年-07月-18日)</t>
+(24年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
           <t>A | 282呎 (1房)
 $594万
 $21,057/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11867,7 +11867,7 @@
           <t>B | 278呎 (1房)
 $559万
 $20,119/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -11875,7 +11875,7 @@
           <t>C | 264呎 (1房)
 $548万
 $20,742/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -11883,7 +11883,7 @@
           <t>D | 210呎 (开放式)
 $430万
 $20,457/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -11891,7 +11891,7 @@
           <t>E | 209呎 (开放式)
 $423万
 $20,230/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -11899,7 +11899,7 @@
           <t>F | 285呎 (1房)
 $744万
 $26,105/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -11907,7 +11907,7 @@
           <t>G | 211呎 (开放式)
 $648万
 $30,711/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -11915,7 +11915,7 @@
           <t>H | 388呎 (2房)
 $930万
 $23,966/呎
-(23年-02月-23日)</t>
+(23年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11930,7 @@
           <t>A | 282呎 (1房)
 $548万
 $19,418/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11938,7 +11938,7 @@
           <t>B | 278呎 (1房)
 $754万
 $27,104/呎
-(21年-10月-10日)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -11954,7 +11954,7 @@
           <t>D | 210呎 (开放式)
 $428万
 $20,381/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -11962,7 +11962,7 @@
           <t>E | 209呎 (开放式)
 $421万
 $20,148/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -11970,7 +11970,7 @@
           <t>F | 285呎 (1房)
 $783万
 $27,481/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -11978,7 +11978,7 @@
           <t>G | 211呎 (开放式)
 $488万
 $23,114/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -11986,7 +11986,7 @@
           <t>H | 388呎 (2房)
 $991万
 $25,549/呎
-(21年-07月-06日)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
           <t>A | 282呎 (1房)
 $734万
 $26,025/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -12009,7 +12009,7 @@
           <t>B | 278呎 (1房)
 $735万
 $26,424/呎
-(21年-07月-14日)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -12017,7 +12017,7 @@
           <t>C | 264呎 (1房)
 $706万
 $26,723/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -12025,7 +12025,7 @@
           <t>D | 210呎 (开放式)
 $611万
 $29,090/呎
-(24年-03月-25日)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -12033,7 +12033,7 @@
           <t>E | 209呎 (开放式)
 $428万
 $20,478/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12041,7 +12041,7 @@
           <t>F | 285呎 (1房)
 $762万
 $26,737/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -12049,7 +12049,7 @@
           <t>G | 211呎 (开放式)
 $486万
 $23,047/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -12057,7 +12057,7 @@
           <t>H | 388呎 (2房)
 $987万
 $25,443/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
           <t>A | 282呎 (1房)
 $731万
 $25,918/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -12080,7 +12080,7 @@
           <t>B | 277呎 (1房)
 $732万
 $26,408/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -12088,7 +12088,7 @@
           <t>C | 264呎 (1房)
 $698万
 $26,458/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -12096,7 +12096,7 @@
           <t>D | 210呎 (开放式)
 $603万
 $28,700/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -12104,7 +12104,7 @@
           <t>E | 209呎 (开放式)
 $414万
 $19,794/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12112,7 +12112,7 @@
           <t>F | 285呎 (1房)
 $724万
 $25,418/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -12120,7 +12120,7 @@
           <t>G | 211呎 (开放式)
 $582万
 $27,607/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -12128,7 +12128,7 @@
           <t>H | 388呎 (2房)
 $934万
 $24,075/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12143,7 @@
           <t>A | 282呎 (1房)
 $530万
 $18,777/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -12151,7 +12151,7 @@
           <t>B | 277呎 (1房)
 $696万
 $25,108/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -12159,7 +12159,7 @@
           <t>C | 264呎 (1房)
 $659万
 $24,958/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -12167,7 +12167,7 @@
           <t>D | 210呎 (开放式)
 $578万
 $27,543/呎
-(21年-06月-18日)</t>
+(21年-06月-19日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -12175,7 +12175,7 @@
           <t>E | 209呎 (开放式)
 $553万
 $26,450/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -12183,7 +12183,7 @@
           <t>F | 285呎 (1房)
 $756万
 $26,523/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -12191,7 +12191,7 @@
           <t>G | 211呎 (开放式)
 $592万
 $28,047/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -12199,7 +12199,7 @@
           <t>H | 388呎 (2房)
 $970万
 $24,995/呎
-(22年-01月-18日)</t>
+(22年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
           <t>A | 282呎 (1房)
 $527万
 $18,699/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -12222,7 +12222,7 @@
           <t>B | 277呎 (1房)
 $719万
 $25,942/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -12230,7 +12230,7 @@
           <t>C | 264呎 (1房)
 $659万
 $24,951/呎
-(22年-03月-02日)</t>
+(22年-03月-03日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -12238,7 +12238,7 @@
           <t>D | 210呎 (开放式)
 $570万
 $27,162/呎
-(21年-07月-20日)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -12246,7 +12246,7 @@
           <t>E | 209呎 (开放式)
 $590万
 $28,225/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -12254,7 +12254,7 @@
           <t>F | 285呎 (1房)
 $712万
 $24,965/呎
-(21年-06月-18日)</t>
+(21年-06月-19日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -12262,7 +12262,7 @@
           <t>G | 211呎 (开放式)
 $557万
 $26,408/呎
-(21年-10月-07日)</t>
+(21年-10月-08日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -12270,7 +12270,7 @@
           <t>H | 388呎 (2房)
 $961万
 $24,771/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -12285,7 +12285,7 @@
           <t>A | 283呎 (1房)
 $689万
 $24,360/呎
-(22年-01月-26日)</t>
+(22年-01月-27日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -12293,7 +12293,7 @@
           <t>B | 278呎 (1房)
 $683万
 $24,576/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -12301,7 +12301,7 @@
           <t>C | 264呎 (1房)
 $610万
 $23,098/呎
-(21年-06月-18日)</t>
+(21年-06月-19日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -12309,7 +12309,7 @@
           <t>D | 210呎 (开放式)
 $581万
 $27,667/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -12317,7 +12317,7 @@
           <t>E | 209呎 (开放式)
 $543万
 $25,976/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -12325,7 +12325,7 @@
           <t>F | 285呎 (1房)
 $742万
 $26,049/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -12333,7 +12333,7 @@
           <t>G | 211呎 (开放式)
 $555万
 $26,303/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -12341,7 +12341,7 @@
           <t>H | 388呎 (2房)
 $957万
 $24,673/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -12356,7 +12356,7 @@
           <t>A | 283呎 (1房)
 $689万
 $24,336/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -12364,7 +12364,7 @@
           <t>B | 277呎 (1房)
 $701万
 $25,292/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -12372,7 +12372,7 @@
           <t>C | 264呎 (1房)
 $635万
 $24,045/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -12380,7 +12380,7 @@
           <t>D | 210呎 (开放式)
 $531万
 $25,281/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -12388,7 +12388,7 @@
           <t>E | 209呎 (开放式)
 $570万
 $27,249/呎
-(24年-03月-19日)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -12396,7 +12396,7 @@
           <t>F | 285呎 (1房)
 $708万
 $24,842/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -12404,7 +12404,7 @@
           <t>G | 211呎 (开放式)
 $581万
 $27,526/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -12412,7 +12412,7 @@
           <t>H | 388呎 (2房)
 $924万
 $23,807/呎
-(22年-08月-08日)</t>
+(22年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
           <t>A | 283呎 (1房)
 $716万
 $25,318/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12435,7 +12435,7 @@
           <t>B | 277呎 (1房)
 $672万
 $24,260/呎
-(22年-02月-13日)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -12443,7 +12443,7 @@
           <t>C | 264呎 (1房)
 $660万
 $25,011/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -12451,7 +12451,7 @@
           <t>D | 209呎 (开放式)
 $531万
 $25,407/呎
-(22年-04月-13日)</t>
+(22年-04月-14日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -12459,7 +12459,7 @@
           <t>E | 209呎 (开放式)
 $553万
 $26,459/呎
-(21年-06月-18日)</t>
+(21年-06月-19日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -12467,7 +12467,7 @@
           <t>F | 286呎 (1房)
 $718万
 $25,108/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -12483,7 +12483,7 @@
           <t>H | 388呎 (2房)
 $950万
 $24,477/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
           <t>A | 282呎 (1房)
 $714万
 $25,305/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12506,7 +12506,7 @@
           <t>B | 277呎 (1房)
 $693万
 $25,007/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12514,7 +12514,7 @@
           <t>C | 264呎 (1房)
 $658万
 $24,905/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -12522,7 +12522,7 @@
           <t>D | 209呎 (开放式)
 $522万
 $24,995/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -12530,7 +12530,7 @@
           <t>E | 209呎 (开放式)
 $563万
 $26,938/呎
-(24年-03月-21日)</t>
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -12538,7 +12538,7 @@
           <t>F | 286呎 (1房)
 $703万
 $24,566/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -12546,7 +12546,7 @@
           <t>G | 211呎 (开放式)
 $548万
 $25,986/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -12554,7 +12554,7 @@
           <t>H | 388呎 (2房)
 $946万
 $24,376/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
           <t>A | 282呎 (1房)
 $711万
 $25,199/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -12577,7 +12577,7 @@
           <t>B | 277呎 (1房)
 $658万
 $23,765/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -12585,7 +12585,7 @@
           <t>C | 264呎 (1房)
 $655万
 $24,799/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -12593,7 +12593,7 @@
           <t>D | 209呎 (开放式)
 $524万
 $25,053/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -12601,7 +12601,7 @@
           <t>E | 209呎 (开放式)
 $523万
 $25,033/呎
-(21年-06月-18日)</t>
+(21年-06月-19日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -12609,7 +12609,7 @@
           <t>F | 286呎 (1房)
 $733万
 $25,633/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -12617,7 +12617,7 @@
           <t>G | 211呎 (开放式)
 $572万
 $27,109/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -12625,7 +12625,7 @@
           <t>H | 388呎 (2房)
 $899万
 $23,175/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
     </row>

--- a/九龙-何文田-VAU Residence/VAU Residence_销控明细表.xlsx
+++ b/九龙-何文田-VAU Residence/VAU Residence_销控明细表.xlsx
@@ -9612,7 +9612,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -11093,17 +11093,17 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -12470,12 +12470,12 @@
 (21年-07月-06日)</t>
         </is>
       </c>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 211呎 (开放式)
 $655万
 $31,057/呎
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">

--- a/九龙-何文田-VAU Residence/VAU Residence_销控明细表.xlsx
+++ b/九龙-何文田-VAU Residence/VAU Residence_销控明细表.xlsx
@@ -9612,34 +9612,34 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>6553000</v>
+        <v>6095000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>31057</v>
+        <v>28886</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>5897700</v>
+        <v>6095000</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>27951</v>
+        <v>28886</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -12470,12 +12470,12 @@
 (21年-07月-06日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>G | 211呎 (开放式)
-$655万
-$31,057/呎
-(已定价未售)</t>
+$610万
+$28,886/呎
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">

--- a/九龙-何文田-VAU Residence/VAU Residence_销控明细表.xlsx
+++ b/九龙-何文田-VAU Residence/VAU Residence_销控明细表.xlsx
@@ -9617,7 +9617,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -12475,7 +12475,7 @@
           <t>G | 211呎 (开放式)
 $610万
 $28,886/呎
-(26年-08月-05日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
